--- a/public/downloads/Import_cong_viec_NV.xlsx
+++ b/public/downloads/Import_cong_viec_NV.xlsx
@@ -524,13 +524,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="3"/>
+    <col width="46" customWidth="1" min="2" max="3"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="7" min="4" max="5"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="11"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -621,17 +621,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Tiếp nhận, kiểm tra tính hợp pháp, hợp lệ của chứng từ thu chi, đề nghị thanh toán theo Quy chế chi tiêu nội bộ</t>
+          <t>Rút dự toán thanh toán tiền lương, các khoản phụ cấp tháng 6/2026 cho cán bộ, giáo viên, nhân viên đúng thời hạn</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>N1_594 - Thu thập và xử lý thông tin số liệu chứng từ kế toán</t>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,27 +645,27 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Bộ chứng từ thanh toán thu - chi lưu tại phòng Tài chính - Kế toán</t>
+          <t>Giấy rút dự toán ngân sách và bảng thanh toán lương tháng 6/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Lập phiếu thu, phiếu chi, giấy đề nghị rút hạn mức, ủy nhiệm chi và cập nhật số liệu chính xác vào phần mềm MISA</t>
+          <t>Tiếp nhận, đăng ký, chuyển giao kịp thời văn bản chỉ đạo của Sở về thi tốt nghiệp THPT và tuyển sinh lớp 10 năm 2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>N1_594 - Thu thập và xử lý thông tin số liệu chứng từ kế toán</t>
+          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Dữ liệu kế toán xuất từ phần mềm MISA</t>
+          <t>Sổ theo dõi văn bản đến tháng 6/2026 trên iOffice</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Lập hồ sơ rút dự toán thanh toán tiền lương, các khoản phụ cấp, chế độ bảo hiểm xã hội, BHYT, KPCĐ đúng hạn hàng tháng</t>
+          <t>Chuẩn bị cơ số thuốc, vật tư y tế, phòng y tế phục vụ Điểm thi tốt nghiệp THPT năm 2026 tại trường an toàn</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,27 +713,27 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Bảng thanh toán tiền lương có chữ ký và xác nhận của KBNN</t>
+          <t>Biên bản kiểm tra điều kiện y tế phục vụ kỳ thi tốt nghiệp 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Đối chiếu số liệu tài khoản tiền gửi, tiền dự toán ngân sách định kỳ hàng tháng, quý với Kho bạc Nhà nước</t>
+          <t>Bảo dưỡng, kiểm tra hệ thống máy vi tính, đường truyền internet, camera giám sát phục vụ thi tốt nghiệp THPT 2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
+          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Biên bản xác nhận số dư tài khoản tại Kho bạc Nhà nước</t>
+          <t>Nhật ký kiểm tra thiết bị CNTT phục vụ kỳ thi</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Lập báo cáo quyết toán tài chính ngân sách năm học và quyết toán ngân sách nhà nước năm đúng hạn</t>
+          <t>Thu hồi SGK, tài liệu tham khảo cho mượn năm học 2025 - 2026; xử lý kỹ thuật và sắp xếp lại kho sách thư viện</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
+          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>31/01/2027</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính năm 2026 gửi Sở GD&amp;ĐT và Kho bạc</t>
+          <t>Sổ theo dõi mượn trả sách thư viện cuối năm</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện công khai tài chính quý, năm và phục vụ chu đáo các đợt thanh tra, kiểm tra, kiểm toán tài chính</t>
+          <t>Thực hiện đối chiếu số dư tài khoản tiền gửi và hạn mức kinh phí 6 tháng đầu năm 2026 với Kho bạc Nhà nước</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Biểu mẫu công khai tài chính niêm yết tại bảng tin cơ quan</t>
+          <t>Biên bản đối chiếu tài khoản với KBNN kỳ 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Tiếp nhận, đăng ký, chuyển giao kịp thời văn bản đến trên hệ thống quản lý văn bản iOffice/VNPT iOffice</t>
+          <t>Lập báo cáo tài chính và báo cáo quyết toán ngân sách nhà nước 6 tháng đầu năm 2026 nộp Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
+          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,27 +849,27 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi văn bản đến và dữ liệu trên phần mềm quản lý văn bản</t>
+          <t>Báo cáo quyết toán ngân sách 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra thể thức, lấy số, phát hành văn bản đi của nhà trường đảm bảo đúng quy chuẩn kỹ thuật văn bản</t>
+          <t>Tiếp nhận hồ sơ, sao lục học bạ và cấp phát giấy chứng nhận tốt nghiệp tạm thời cho học sinh khối 12 năm 2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
+          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Sổ văn bản đi năm học 2026-2027</t>
+          <t>Sổ cấp phát văn bằng chứng chỉ, giấy chứng nhận tốt nghiệp tạm thời</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Quản lý và sử dụng con dấu, USB token chữ ký số cơ quan an toàn, chặt chẽ, đúng thẩm quyền</t>
+          <t>Thu thập, phân loại và lưu trữ toàn bộ hồ sơ thi tốt nghiệp THPT 2026, hồ sơ tuyển sinh 10 và hồ sơ thi đua năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
+          <t>N1_604 - Thu thập hồ sơ tài liệu vào kho lưu trữ, phục vụ khai thác, sử dụng tài liệu lưu trữ</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi đóng dấu và nhật ký ký số điện tử</t>
+          <t>Mục lục hồ sơ tài liệu nộp lưu trữ cơ quan đợt hè 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện tiếp nhận và giải quyết thủ tục hành chính: cấp bản sao học bạ, giấy chứng nhận tốt nghiệp cho học sinh đúng hạn</t>
+          <t>Chi trả kịp thời tiền làm nhiệm vụ coi thi, chấm thi và tiền phụ cấp làm việc hè cho cán bộ, giáo viên đúng danh sách</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
+          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,27 +951,27 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Sổ cấp phát văn bằng chứng chỉ, giấy chứng nhận</t>
+          <t>Bảng thanh toán tiền làm nhiệm vụ thi có chữ ký người nhận</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Thu thập, phân loại, chỉnh lý hồ sơ thi đua, bài thi tốt nghiệp, sổ điểm của các năm học đưa vào kho lưu trữ</t>
+          <t>Lập dự toán kinh phí mua sắm, sửa chữa cơ sở vật chất, bàn ghế phục vụ khai giảng và năm học mới 2026 - 2027</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>N1_604 - Thu thập hồ sơ tài liệu vào kho lưu trữ, phục vụ khai thác, sử dụng tài liệu lưu trữ</t>
+          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,27 +985,27 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Danh mục hồ sơ tài liệu nộp lưu trữ cơ quan năm học</t>
+          <t>Dự toán chi tiết mua sắm, sửa chữa CSVC đầu năm học mới</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Bảo quản an toàn kho tài liệu lưu trữ, chống ẩm, mối mọt; phục vụ tra cứu hồ sơ nhanh chóng, chính xác</t>
+          <t>Kiểm kê, vệ sinh, bảo dưỡng toàn bộ thiết bị dạy học, hóa chất, phòng thực hành Lý, Hóa, Sinh trong dịp hè</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>N1_604 - Thu thập hồ sơ tài liệu vào kho lưu trữ, phục vụ khai thác, sử dụng tài liệu lưu trữ</t>
+          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Nhật ký khai thác, sử dụng tài liệu lưu trữ</t>
+          <t>Biên bản kiểm kê thiết bị dạy học và phòng bộ môn hè 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Quản lý quỹ tiền mặt tuyệt đối an toàn; thực hiện thu - chi tiền mặt chính xác, kịp thời theo lệnh thu - chi hợp lệ</t>
+          <t>Tiếp nhận, đóng dấu nghiệp vụ và cấp phát SGK mới, tài liệu hướng dẫn giảng dạy cho GV và HS chuẩn bị năm học mới</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
+          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Sổ quỹ tiền mặt có đối chiếu hàng ngày giữa Thủ quỹ và Kế toán</t>
+          <t>Sổ đăng ký cá biệt và danh sách cấp phát sách giáo khoa mới</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Chi trả kịp thời tiền học bổng, tiền hỗ trợ chi phí học tập cho học sinh diện chính sách, vùng cao đầy đủ chữ ký</t>
+          <t>Bảo dưỡng phòng máy tính tin học, kiểm tra tài khoản VnEdu, CSDL ngành, học bạ số và chữ ký số chuẩn bị năm học mới</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
+          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Danh sách học sinh nhận tiền chính sách có chữ ký người nhận</t>
+          <t>Biên bản kiểm tra hệ thống CNTT và phần mềm quản lý trường học</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Lập kế hoạch quản lý, bảo dưỡng và chuẩn bị thiết bị, hóa chất phục vụ các tiết dạy thực hành môn Lý, Hóa, Sinh</t>
+          <t>Lập hồ sơ rút dự toán thanh toán tiền lương, phụ cấp tháng 9/2026 và trích nộp BHXH, BHYT, KPCĐ đúng thời hạn</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Sổ mượn trả thiết bị và nhật ký sử dụng phòng thí nghiệm</t>
+          <t>Bảng thanh toán lương tháng 9/2026 và chứng từ nộp bảo hiểm xã hội</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện kiểm kê tài sản thiết bị định kỳ; đề xuất mua sắm bổ sung thiết bị dạy học tối thiểu và thanh lý đồ hỏng</t>
+          <t>Kiểm tra thể thức, lấy số, phát hành các quyết định phân công chuyên môn, kế hoạch khai giảng và văn bản đầu năm học</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
+          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm kê thiết bị dạy học cuối kỳ/năm</t>
+          <t>Sổ theo dõi văn bản đi tháng 9/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Quản lý kho sách, cấp phát SGK, SGV và tài liệu tham khảo cho giáo viên, học sinh ngay đầu năm học mới</t>
+          <t>Quản lý con dấu, chứng thư số; thực hiện đóng dấu giấy xác nhận học sinh, chứng chỉ cho học sinh đầu năm đúng quy định</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
+          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Sổ đăng ký cá biệt, sổ mượn trả sách thư viện</t>
+          <t>Sổ cấp giấy xác nhận học sinh năm học 2026-2027</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động hưởng ứng Ngày Sách và Văn hóa đọc Việt Nam, tuyên truyền giới thiệu sách hay cho học sinh</t>
+          <t>Mở sổ quỹ tiền mặt năm học 2026 - 2027, ghi chép thu chi quỹ tháng 9 chính xác, thực hiện kiểm kê quỹ cuối tháng</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
+          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>30/04/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,27 +1223,27 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch và báo cáo tổ chức Ngày hội đọc sách năm học</t>
+          <t>Sổ quỹ tiền mặt tháng 9/2026 có xác nhận của Kế toán và Hiệu trưởng</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Quản lý tủ thuốc y tế trường học; lập kế hoạch và tổ chức sơ cứu, chăm sóc sức khỏe ban đầu cho học sinh và cán bộ</t>
+          <t>Lập kế hoạch sử dụng phòng học bộ môn và chuẩn bị đầy đủ thiết bị, hóa chất phục vụ các tiết dạy thực hành tháng 9</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi khám chữa bệnh và cấp phát thuốc sơ cứu</t>
+          <t>Sổ mượn trả thiết bị dạy học tháng 9/2026</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Tuyên truyền phòng chống dịch bệnh theo mùa, vệ sinh an toàn thực phẩm, vận động học sinh tham gia BHYT đạt 100%</t>
+          <t>Kiểm tra tủ thuốc y tế, bổ sung bông băng thuốc thiết yếu và lập kế hoạch chăm sóc sức khỏe học sinh đầu năm học mới</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1291,27 +1291,27 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo y tế học đường và tỷ lệ học sinh tham gia BHYT đạt 100%</t>
+          <t>Kế hoạch y tế học đường năm học 2026-2027 và danh mục thuốc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Quản trị, vận hành hệ thống mạng internet, phòng máy tính tin học, bảo đảm kết nối thông suốt phục vụ học tập và thi</t>
+          <t>Tuyên truyền phòng chống sốt xuất huyết, dịch bệnh mùa thu và phối hợp vận động học sinh tham gia BHYT đạt 100%</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Nhật ký vận hành phòng máy tính và bảo dưỡng định kỳ hệ thống mạng</t>
+          <t>Báo cáo công tác BHYT học sinh tháng 9/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Quản trị kỹ thuật cổng thông tin điện tử (website) nhà trường, hỗ trợ kỹ thuật phần mềm CSDL, học bạ số và chữ ký số</t>
+          <t>Đưa tin bài, hình ảnh Lễ Khai giảng năm học 2026 - 2027 lên website trường; sao lưu an toàn CSDL tháng 9/2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo an toàn thông tin và dữ liệu sao lưu định kỳ hệ thống</t>
+          <t>Link bài viết trên website trường và file nhật ký sao lưu hệ thống</t>
         </is>
       </c>
     </row>

--- a/public/downloads/Import_cong_viec_NV.xlsx
+++ b/public/downloads/Import_cong_viec_NV.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L75"/>
+  <dimension ref="A2:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Rút dự toán thanh toán tiền lương, các khoản phụ cấp tháng 6/2026 cho cán bộ, giáo viên, nhân viên đúng thời hạn</t>
+          <t>Rút dự toán thanh toán tiền lương, các khoản phụ cấp tháng 5/2026 và kinh phí hoạt động chuyên môn cuối năm học đúng quy định</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Giấy rút dự toán ngân sách và bảng thanh toán lương tháng 6/2026</t>
+          <t>Giấy rút dự toán ngân sách và bảng thanh toán lương tháng 5/2026</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Tiếp nhận, đăng ký, chuyển giao kịp thời văn bản chỉ đạo của Sở về thi tốt nghiệp THPT và tuyển sinh lớp 10 năm 2026</t>
+          <t>Tiếp nhận, xử lý và phân phối kịp thời văn bản chỉ đạo của Sở GD&amp;ĐT về thi tốt nghiệp, tuyển sinh 10 và tổng kết năm học</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi văn bản đến tháng 6/2026 trên iOffice</t>
+          <t>Sổ theo dõi văn bản đến tháng 5/2026 trên iOffice</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Chuẩn bị cơ số thuốc, vật tư y tế, phòng y tế phục vụ Điểm thi tốt nghiệp THPT năm 2026 tại trường an toàn</t>
+          <t>Kiểm tra, đóng dấu xác nhận và ký số học bạ số, phiếu điểm cho học sinh lớp 12 phục vụ hồ sơ đăng ký dự thi tốt nghiệp và xét tuyển ĐH</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm tra điều kiện y tế phục vụ kỳ thi tốt nghiệp 2026</t>
+          <t>Sổ theo dõi đóng dấu học bạ và chứng nhận học sinh khối 12</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Bảo dưỡng, kiểm tra hệ thống máy vi tính, đường truyền internet, camera giám sát phục vụ thi tốt nghiệp THPT 2026</t>
+          <t>Quản trị kỹ thuật CSDL ngành, kiểm tra đường truyền và hỗ trợ học sinh khối 12 đăng ký dự thi tốt nghiệp trực tuyến trên Cổng dịch vụ công</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Nhật ký kiểm tra thiết bị CNTT phục vụ kỳ thi</t>
+          <t>Nhật ký hỗ trợ kỹ thuật đăng ký dự thi trực tuyến</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Thu hồi SGK, tài liệu tham khảo cho mượn năm học 2025 - 2026; xử lý kỹ thuật và sắp xếp lại kho sách thư viện</t>
+          <t>Phục vụ thiết bị âm thanh, ánh sáng, phòng thi cho kỳ kiểm tra cuối kỳ II và Lễ Bế giảng năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
+          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,27 +781,27 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi mượn trả sách thư viện cuối năm</t>
+          <t>Sổ theo dõi bàn giao thiết bị phục vụ kỳ thi và sự kiện bế giảng</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện đối chiếu số dư tài khoản tiền gửi và hạn mức kinh phí 6 tháng đầu năm 2026 với Kho bạc Nhà nước</t>
+          <t>Lập danh sách, thông báo và thực hiện tiếp nhận thu hồi SGK, tài liệu tham khảo cho mượn năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
+          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Biên bản đối chiếu tài khoản với KBNN kỳ 6 tháng đầu năm 2026</t>
+          <t>Sổ theo dõi thu hồi sách giáo khoa mượn của học sinh</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Lập báo cáo tài chính và báo cáo quyết toán ngân sách nhà nước 6 tháng đầu năm 2026 nộp Sở GD&amp;ĐT</t>
+          <t>Kiểm tra tủ thuốc y tế, chuẩn bị thuốc sơ cấp cứu phục vụ thi cuối kỳ II, thi thử tốt nghiệp và tuyên truyền phòng chống say nắng, đuối nước</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo quyết toán ngân sách 6 tháng đầu năm 2026</t>
+          <t>Nhật ký chăm sóc sức khỏe học sinh và biên bản kiểm tra y tế</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Tiếp nhận hồ sơ, sao lục học bạ và cấp phát giấy chứng nhận tốt nghiệp tạm thời cho học sinh khối 12 năm 2026</t>
+          <t>Thực hiện thanh toán tiền coi kiểm tra cuối kỳ, khen thưởng học sinh đạt giải năm học 2025 - 2026 và kiểm kê quỹ tiền mặt tháng 5</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
+          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,27 +883,27 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Sổ cấp phát văn bằng chứng chỉ, giấy chứng nhận tốt nghiệp tạm thời</t>
+          <t>Phiếu chi khen thưởng và biên bản kiểm kê quỹ tháng 5/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Thu thập, phân loại và lưu trữ toàn bộ hồ sơ thi tốt nghiệp THPT 2026, hồ sơ tuyển sinh 10 và hồ sơ thi đua năm học 2025 - 2026</t>
+          <t>Rút dự toán thanh toán tiền lương, các khoản phụ cấp tháng 6/2026 cho cán bộ, giáo viên, nhân viên đúng thời hạn</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N1_604 - Thu thập hồ sơ tài liệu vào kho lưu trữ, phục vụ khai thác, sử dụng tài liệu lưu trữ</t>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Mục lục hồ sơ tài liệu nộp lưu trữ cơ quan đợt hè 2026</t>
+          <t>Giấy rút dự toán ngân sách và bảng thanh toán lương tháng 6/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Chi trả kịp thời tiền làm nhiệm vụ coi thi, chấm thi và tiền phụ cấp làm việc hè cho cán bộ, giáo viên đúng danh sách</t>
+          <t>Tiếp nhận, đăng ký, chuyển giao kịp thời văn bản chỉ đạo của Sở về thi tốt nghiệp THPT và tuyển sinh lớp 10 năm 2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
+          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Bảng thanh toán tiền làm nhiệm vụ thi có chữ ký người nhận</t>
+          <t>Sổ theo dõi văn bản đến tháng 6/2026 trên iOffice</t>
         </is>
       </c>
     </row>
@@ -961,17 +961,17 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Lập dự toán kinh phí mua sắm, sửa chữa cơ sở vật chất, bàn ghế phục vụ khai giảng và năm học mới 2026 - 2027</t>
+          <t>Chuẩn bị cơ số thuốc, vật tư y tế, phòng y tế phục vụ Điểm thi tốt nghiệp THPT năm 2026 tại trường an toàn</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,27 +985,27 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Dự toán chi tiết mua sắm, sửa chữa CSVC đầu năm học mới</t>
+          <t>Biên bản kiểm tra điều kiện y tế phục vụ kỳ thi tốt nghiệp 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kiểm kê, vệ sinh, bảo dưỡng toàn bộ thiết bị dạy học, hóa chất, phòng thực hành Lý, Hóa, Sinh trong dịp hè</t>
+          <t>Bảo dưỡng, kiểm tra hệ thống máy vi tính, đường truyền internet, camera giám sát phục vụ thi tốt nghiệp THPT 2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
+          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm kê thiết bị dạy học và phòng bộ môn hè 2026</t>
+          <t>Nhật ký kiểm tra thiết bị CNTT phục vụ kỳ thi</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Tiếp nhận, đóng dấu nghiệp vụ và cấp phát SGK mới, tài liệu hướng dẫn giảng dạy cho GV và HS chuẩn bị năm học mới</t>
+          <t>Thu hồi SGK, tài liệu tham khảo cho mượn năm học 2025 - 2026; xử lý kỹ thuật và sắp xếp lại kho sách thư viện</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,27 +1053,27 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Sổ đăng ký cá biệt và danh sách cấp phát sách giáo khoa mới</t>
+          <t>Sổ theo dõi mượn trả sách thư viện cuối năm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Bảo dưỡng phòng máy tính tin học, kiểm tra tài khoản VnEdu, CSDL ngành, học bạ số và chữ ký số chuẩn bị năm học mới</t>
+          <t>Thực hiện đối chiếu số dư tài khoản tiền gửi và hạn mức kinh phí 6 tháng đầu năm 2026 với Kho bạc Nhà nước</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm tra hệ thống CNTT và phần mềm quản lý trường học</t>
+          <t>Biên bản đối chiếu tài khoản với KBNN kỳ 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Lập hồ sơ rút dự toán thanh toán tiền lương, phụ cấp tháng 9/2026 và trích nộp BHXH, BHYT, KPCĐ đúng thời hạn</t>
+          <t>Lập báo cáo tài chính và báo cáo quyết toán ngân sách nhà nước 6 tháng đầu năm 2026 nộp Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
+          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Bảng thanh toán lương tháng 9/2026 và chứng từ nộp bảo hiểm xã hội</t>
+          <t>Báo cáo quyết toán ngân sách 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra thể thức, lấy số, phát hành các quyết định phân công chuyên môn, kế hoạch khai giảng và văn bản đầu năm học</t>
+          <t>Tiếp nhận hồ sơ, sao lục học bạ và cấp phát giấy chứng nhận tốt nghiệp tạm thời cho học sinh khối 12 năm 2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
+          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi văn bản đi tháng 9/2026</t>
+          <t>Sổ cấp phát văn bằng chứng chỉ, giấy chứng nhận tốt nghiệp tạm thời</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Quản lý con dấu, chứng thư số; thực hiện đóng dấu giấy xác nhận học sinh, chứng chỉ cho học sinh đầu năm đúng quy định</t>
+          <t>Thu thập, phân loại và lưu trữ toàn bộ hồ sơ thi tốt nghiệp THPT 2026, hồ sơ tuyển sinh 10 và hồ sơ thi đua năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
+          <t>N1_604 - Thu thập hồ sơ tài liệu vào kho lưu trữ, phục vụ khai thác, sử dụng tài liệu lưu trữ</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Sổ cấp giấy xác nhận học sinh năm học 2026-2027</t>
+          <t>Mục lục hồ sơ tài liệu nộp lưu trữ cơ quan đợt hè 2026</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Mở sổ quỹ tiền mặt năm học 2026 - 2027, ghi chép thu chi quỹ tháng 9 chính xác, thực hiện kiểm kê quỹ cuối tháng</t>
+          <t>Chi trả kịp thời tiền làm nhiệm vụ coi thi, chấm thi và tiền phụ cấp làm việc hè cho cán bộ, giáo viên đúng danh sách</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Sổ quỹ tiền mặt tháng 9/2026 có xác nhận của Kế toán và Hiệu trưởng</t>
+          <t>Bảng thanh toán tiền làm nhiệm vụ thi có chữ ký người nhận</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1233,17 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Lập kế hoạch sử dụng phòng học bộ môn và chuẩn bị đầy đủ thiết bị, hóa chất phục vụ các tiết dạy thực hành tháng 9</t>
+          <t>Lập dự toán kinh phí mua sắm, sửa chữa cơ sở vật chất, bàn ghế phục vụ khai giảng và năm học mới 2026 - 2027</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
+          <t>N3_695 - Tổng hợp và lập báo cáo tài chính hợp nhất, báo cáo quyết toán năm</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Sổ mượn trả thiết bị dạy học tháng 9/2026</t>
+          <t>Dự toán chi tiết mua sắm, sửa chữa CSVC đầu năm học mới</t>
         </is>
       </c>
     </row>
@@ -1267,17 +1267,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra tủ thuốc y tế, bổ sung bông băng thuốc thiết yếu và lập kế hoạch chăm sóc sức khỏe học sinh đầu năm học mới</t>
+          <t>Kiểm kê, vệ sinh, bảo dưỡng toàn bộ thiết bị dạy học, hóa chất, phòng thực hành Lý, Hóa, Sinh trong dịp hè</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch y tế học đường năm học 2026-2027 và danh mục thuốc</t>
+          <t>Biên bản kiểm kê thiết bị dạy học và phòng bộ môn hè 2026</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Tuyên truyền phòng chống sốt xuất huyết, dịch bệnh mùa thu và phối hợp vận động học sinh tham gia BHYT đạt 100%</t>
+          <t>Tiếp nhận, đóng dấu nghiệp vụ và cấp phát SGK mới, tài liệu hướng dẫn giảng dạy cho GV và HS chuẩn bị năm học mới</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+          <t>N2_1067 - Báo cáo kết quả tổ chức thực hiện ngày Sách và Văn hóa đọc Việt Nam năm 2026</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo công tác BHYT học sinh tháng 9/2026</t>
+          <t>Sổ đăng ký cá biệt và danh sách cấp phát sách giáo khoa mới</t>
         </is>
       </c>
     </row>
@@ -1335,113 +1335,305 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
+          <t>Bảo dưỡng phòng máy tính tin học, kiểm tra tài khoản VnEdu, CSDL ngành, học bạ số và chữ ký số chuẩn bị năm học mới</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Biên bản kiểm tra hệ thống CNTT và phần mềm quản lý trường học</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Lập hồ sơ rút dự toán thanh toán tiền lương, phụ cấp tháng 9/2026 và trích nộp BHXH, BHYT, KPCĐ đúng thời hạn</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>N1_599 - Thực hiện giao dịch kho bạc , ngân hàng</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Bảng thanh toán lương tháng 9/2026 và chứng từ nộp bảo hiểm xã hội</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra thể thức, lấy số, phát hành các quyết định phân công chuyên môn, kế hoạch khai giảng và văn bản đầu năm học</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>N1_602 - Quản lý và xử lý văn bản đi, đến (Chính quyền + Đảng ủy)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Sổ theo dõi văn bản đi tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Quản lý con dấu, chứng thư số; thực hiện đóng dấu giấy xác nhận học sinh, chứng chỉ cho học sinh đầu năm đúng quy định</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>N1_603 - Quản lý và sử dụng con dấu, thiết bị lưu khóa bí mật; thực hiện ký số chuyển thủ tục hành chính trên dịch vụ công</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Sổ cấp giấy xác nhận học sinh năm học 2026-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Mở sổ quỹ tiền mặt năm học 2026 - 2027, ghi chép thu chi quỹ tháng 9 chính xác, thực hiện kiểm kê quỹ cuối tháng</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>N1_605 - Quản lý thu, chi tiền mặt tại quỹ, Kiêm nhiệm Thủ quỹ cơ quan; thực hiện các giao dịch tại Kho bạc/Ngân hàng</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Sổ quỹ tiền mặt tháng 9/2026 có xác nhận của Kế toán và Hiệu trưởng</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Lập kế hoạch sử dụng phòng học bộ môn và chuẩn bị đầy đủ thiết bị, hóa chất phục vụ các tiết dạy thực hành tháng 9</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>N4_182 - Tham mưu Quyết đinh quy định định tiêu chuẩn, định mức về máy móc thiết bị dạy học</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Sổ mượn trả thiết bị dạy học tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra tủ thuốc y tế, bổ sung bông băng thuốc thiết yếu và lập kế hoạch chăm sóc sức khỏe học sinh đầu năm học mới</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Kế hoạch y tế học đường năm học 2026-2027 và danh mục thuốc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Tuyên truyền phòng chống sốt xuất huyết, dịch bệnh mùa thu và phối hợp vận động học sinh tham gia BHYT đạt 100%</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>N2_1066 - Báo cáo công tác xây dựng giáo dục môi trường an toàn lành mạnh và phòng chống bạo lực học đường</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Báo cáo công tác BHYT học sinh tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
           <t>Đưa tin bài, hình ảnh Lễ Khai giảng năm học 2026 - 2027 lên website trường; sao lưu an toàn CSDL tháng 9/2026</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>N2_1085 - Triển khai cảnh báo các lỗ hổng bảo mật, an toàn thông tin theo hướng dẫn của cơ quan chuyên môn</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="E38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Link bài viết trên website trường và file nhật ký sao lưu hệ thống</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n"/>
@@ -1813,6 +2005,337 @@
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="10" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="10" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:L2"/>
